--- a/backend/data/financials_by_company/1R6.SI.xlsx
+++ b/backend/data/financials_by_company/1R6.SI.xlsx
@@ -3617,10 +3617,8 @@
           <t>Singapore</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>554859</t>
-        </is>
+      <c r="C2" t="n">
+        <v>554859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3837,7 +3835,7 @@
         <v>-96000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>0.343</v>
@@ -4021,7 +4019,7 @@
         <v>23.809528</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
